--- a/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:15</t>
+          <t>2026-10-14 00:24:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:16</t>
+          <t>2026-10-14 00:24:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:17</t>
+          <t>2026-10-14 00:24:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:19</t>
+          <t>2026-10-14 00:24:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2490</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.79%12,188,000</t>
+          <t>10.73%12,188,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>10.73%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5520</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.53%4,328,000</t>
+          <t>8.45%4,328,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4475</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.18%5,086,000</t>
+          <t>8.05%5,086,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>8.05%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1185</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,27 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.07%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3315</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.17%6,147,000</t>
+          <t>7.21%6,147,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.17%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,27 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.14%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7070</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.22%2,502,000</t>
+          <t>6.26%2,502,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.67%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>627</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.29%2,504,000</t>
+          <t>5.22%23,519,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.22%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2504000</v>
+        <v>23519000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5885</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.01%23,519,000</t>
+          <t>5.21%2,504,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>23519000</v>
+        <v>2504000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1785</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,40 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2050</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.57%8,937,000</t>
+          <t>4.54%6,264,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8937000</v>
+        <v>6264000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1430</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.54%6,264,000</t>
+          <t>4.52%8,937,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.54%</t>
+          <t>4.52%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6264000</v>
+        <v>8937000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,27 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.83%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1735</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.03%6,847,000</t>
+          <t>4.20%6,847,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>142</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:45</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,35 +1302,33 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.64%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.37%4,315,561</t>
+          <t>2.45%3,281,561</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4315561</v>
+        <v>3281561</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,42 +1354,42 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2260</v>
+        <v>1260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.32%2,887,848</t>
+          <t>2.42%5,423,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2887848</v>
+        <v>5423000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1447,38 +1419,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.89%</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>740</v>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.20%8,348,000</t>
+          <t>2.28%2,887,848</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>8348000</v>
+        <v>2887848</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1495,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1508,38 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>8095</v>
+          <t>+0.95%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%684,000</t>
+          <t>2.21%8,348,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>684000</v>
+        <v>8348000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1556,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1569,38 +1545,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.26%</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1170</v>
+          <t>+1.85%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8245</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.56%3,741,000</t>
+          <t>2.19%751,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3741000</v>
+        <v>751000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1617,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1635,33 +1613,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.95%</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>17350</v>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.97%157,900</t>
+          <t>1.16%186,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>157900</v>
+        <v>186900</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1678,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1696,33 +1676,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.24%3275</t>
+          <t>-1.53%3225</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.24%</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>3275</v>
+          <t>-1.53%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.49%420,000</t>
+          <t>0.54%470,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>420000</v>
+        <v>470000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1739,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1757,25 +1739,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.67%</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>305</v>
+          <t>-2.79%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>296.5</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.45%4,143,450</t>
+          <t>0.43%4,143,450</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1783,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1800,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1813,34 +1797,36 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.64%</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>2210</v>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.39%499,000</t>
+          <t>0.41%696,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>499000</v>
+        <v>696000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1861,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1874,34 +1860,36 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1715</v>
+          <t>-0.68%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.35%576,000</t>
+          <t>0.39%499,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>576000</v>
+        <v>499000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1922,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1935,38 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.03%240</t>
+          <t>+9.91%588</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.03%</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>240</v>
+          <t>+9.91%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.19%2,185,000</t>
+          <t>0.20%957,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2185000</v>
+        <v>957000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1983,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1996,25 +1986,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.39%5700</t>
+          <t>+0.83%242</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.39%</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>5700</v>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.19%93,000</t>
+          <t>0.19%2,185,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2023,11 +2015,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>93000</v>
+        <v>2185000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2044,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2057,34 +2049,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.67%838</t>
+          <t>-1.49%5615</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.67%</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>838</v>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5615</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.14%478,000</t>
+          <t>0.18%93,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>478000</v>
+        <v>93000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2105,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2118,34 +2112,36 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.1%96.4</t>
+          <t>+1.79%853</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.1%</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>96.40000000000001</v>
+          <t>+1.79%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.13%3,921,000</t>
+          <t>0.14%478,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3921000</v>
+        <v>478000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2166,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2179,34 +2175,36 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3376新日興</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.02%169.5</t>
+          <t>-1.04%95.4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.02%</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>169.5</v>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.10%1,740,000</t>
+          <t>0.13%3,921,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1740000</v>
+        <v>3921000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2227,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:50</t>
+          <t>2026-10-14 21:52:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2240,38 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>+3.54%278</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.48%</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1600</v>
+          <t>+3.54%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.07%121,000</t>
+          <t>0.12%1,257,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>121000</v>
+        <v>1257000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.26%19.15</t>
+          <t>+5.6%179</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>19.15</v>
+        <v>179</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.04%5,163,000</t>
+          <t>0.11%1,740,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>5163000</v>
+        <v>1740000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,34 +2362,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.37%243.5</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>243.5</v>
+        <v>1540</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0.07%121,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>501000</v>
+        <v>121000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,34 +2423,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.47%268.5</t>
+          <t>+1.83%19.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>268.5</v>
+        <v>19.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.04%5,163,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.12%264</t>
+          <t>+2.87%250.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>264</v>
+        <v>250.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,21 +2545,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.56%493</t>
+          <t>+9.85%290</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>493</v>
+        <v>290</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,21 +2606,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-7.74%4055</t>
+          <t>+1.83%502</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4055</v>
+        <v>502</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.49%81.4</t>
+          <t>-2.84%3940</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>81.40000000000001</v>
+        <v>3940</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.31%1170</t>
+          <t>+0.37%81.7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1170</v>
+        <v>81.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>+1.28%1185</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7275</v>
+        <v>1185</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>552</v>
+        <v>6880</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.31%323</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>323</v>
+        <v>567</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-8.08%535</t>
+          <t>0%323</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.08%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>535</v>
+        <v>323</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>488</v>
+        <v>480.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.98%103</t>
+          <t>+0.49%103.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:51</t>
+          <t>2026-10-14 21:52:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-8.97%1015</t>
+          <t>+0.49%1020</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.97%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.08%547</t>
+          <t>+2.56%561</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-5.69%116</t>
+          <t>+0.86%117</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.31%175</t>
+          <t>+0.57%176</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:24:53</t>
+          <t>2026-10-14 21:53:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-5.26%162</t>
+          <t>+2.47%166</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+2.47%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:42</t>
+          <t>2026-10-14 22:00:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:44</t>
+          <t>2026-10-14 22:00:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:52:55</t>
+          <t>2026-10-14 22:00:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:06</t>
+          <t>2026-10-14 22:00:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:45</t>
+          <t>2026-10-14 22:30:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:47</t>
+          <t>2026-10-14 22:30:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:52</t>
+          <t>2026-10-14 22:30:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:53</t>
+          <t>2026-10-14 22:30:49</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
